--- a/research/traditional_assets/database/data/spain/spain_software_internet.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_software_internet.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.434</v>
+        <v>0.618</v>
       </c>
       <c r="G2">
-        <v>0.08051575931232093</v>
+        <v>0.1808346213292117</v>
       </c>
       <c r="H2">
-        <v>0.06361031518624642</v>
+        <v>0.1808346213292117</v>
       </c>
       <c r="I2">
-        <v>-0.03817196639972806</v>
+        <v>-0.06555397664028401</v>
       </c>
       <c r="J2">
-        <v>-0.03817196639972806</v>
+        <v>-0.06555397664028401</v>
       </c>
       <c r="K2">
-        <v>-2.56</v>
+        <v>-6.83</v>
       </c>
       <c r="L2">
-        <v>-0.07335243553008597</v>
+        <v>-0.105564142194745</v>
       </c>
       <c r="M2">
-        <v>0.053</v>
+        <v>0.55</v>
       </c>
       <c r="N2">
-        <v>0.000374029640084686</v>
+        <v>0.00435471100554236</v>
       </c>
       <c r="O2">
-        <v>-0.020703125</v>
+        <v>-0.08052708638360176</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.053</v>
+        <v>0.55</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>11.6</v>
+        <v>16</v>
       </c>
       <c r="V2">
-        <v>0.08186309103740297</v>
+        <v>0.1266825019794141</v>
       </c>
       <c r="W2">
-        <v>-0.4507042253521127</v>
+        <v>-0.1206713780918728</v>
       </c>
       <c r="X2">
-        <v>0.09010364597895985</v>
+        <v>0.1878682728384909</v>
       </c>
       <c r="Y2">
-        <v>-0.5408078713310726</v>
+        <v>-0.3085396509303637</v>
       </c>
       <c r="Z2">
-        <v>3.231179863780114</v>
+        <v>1.847689212765585</v>
       </c>
       <c r="AA2">
-        <v>-0.1233404891916924</v>
+        <v>-0.1211233754921399</v>
       </c>
       <c r="AB2">
-        <v>0.0763174057481389</v>
+        <v>0.14335396086642</v>
       </c>
       <c r="AC2">
-        <v>-0.1996578949398313</v>
+        <v>-0.2644773363585599</v>
       </c>
       <c r="AD2">
-        <v>40.1</v>
+        <v>59</v>
       </c>
       <c r="AE2">
-        <v>0.08100813675254696</v>
+        <v>1.316711443131878</v>
       </c>
       <c r="AF2">
-        <v>40.18100813675255</v>
+        <v>60.31671144313188</v>
       </c>
       <c r="AG2">
-        <v>28.58100813675254</v>
+        <v>44.31671144313188</v>
       </c>
       <c r="AH2">
-        <v>0.2209192072794169</v>
+        <v>0.3232117369162425</v>
       </c>
       <c r="AI2">
-        <v>0.4151745152310913</v>
+        <v>0.584936336690645</v>
       </c>
       <c r="AJ2">
-        <v>0.1678461294626536</v>
+        <v>0.2597442599161985</v>
       </c>
       <c r="AK2">
-        <v>0.3355326352896364</v>
+        <v>0.5087050545068036</v>
       </c>
       <c r="AL2">
-        <v>0.911</v>
+        <v>0.951</v>
       </c>
       <c r="AM2">
-        <v>0.909</v>
+        <v>0.95</v>
       </c>
       <c r="AN2">
-        <v>6.411896386312761</v>
+        <v>4.757297210127399</v>
       </c>
       <c r="AO2">
-        <v>-1.536772777167947</v>
+        <v>-4.921135646687697</v>
       </c>
       <c r="AP2">
-        <v>4.570036478534146</v>
+        <v>3.573351995092072</v>
       </c>
       <c r="AQ2">
-        <v>-1.54015401540154</v>
+        <v>-4.926315789473684</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +719,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.434</v>
+        <v>0.618</v>
       </c>
       <c r="G3">
-        <v>0.08051575931232093</v>
+        <v>0.1808346213292117</v>
       </c>
       <c r="H3">
-        <v>0.06361031518624642</v>
+        <v>0.1808346213292117</v>
       </c>
       <c r="I3">
-        <v>-0.03817196639972806</v>
+        <v>-0.06555397664028401</v>
       </c>
       <c r="J3">
-        <v>-0.03817196639972806</v>
+        <v>-0.06555397664028401</v>
       </c>
       <c r="K3">
-        <v>-2.56</v>
+        <v>-6.83</v>
       </c>
       <c r="L3">
-        <v>-0.07335243553008597</v>
+        <v>-0.105564142194745</v>
       </c>
       <c r="M3">
-        <v>0.053</v>
+        <v>0.55</v>
       </c>
       <c r="N3">
-        <v>0.000374029640084686</v>
+        <v>0.00435471100554236</v>
       </c>
       <c r="O3">
-        <v>-0.020703125</v>
+        <v>-0.08052708638360176</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +758,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.053</v>
+        <v>0.55</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>11.6</v>
+        <v>16</v>
       </c>
       <c r="V3">
-        <v>0.08186309103740297</v>
+        <v>0.1266825019794141</v>
       </c>
       <c r="W3">
-        <v>-0.4507042253521127</v>
+        <v>-0.1206713780918728</v>
       </c>
       <c r="X3">
-        <v>0.09010364597895985</v>
+        <v>0.1878682728384909</v>
       </c>
       <c r="Y3">
-        <v>-0.5408078713310726</v>
+        <v>-0.3085396509303637</v>
       </c>
       <c r="Z3">
-        <v>3.231179863780114</v>
+        <v>1.847689212765585</v>
       </c>
       <c r="AA3">
-        <v>-0.1233404891916924</v>
+        <v>-0.1211233754921399</v>
       </c>
       <c r="AB3">
-        <v>0.0763174057481389</v>
+        <v>0.14335396086642</v>
       </c>
       <c r="AC3">
-        <v>-0.1996578949398313</v>
+        <v>-0.2644773363585599</v>
       </c>
       <c r="AD3">
-        <v>40.1</v>
+        <v>59</v>
       </c>
       <c r="AE3">
-        <v>0.08100813675254696</v>
+        <v>1.316711443131878</v>
       </c>
       <c r="AF3">
-        <v>40.18100813675255</v>
+        <v>60.31671144313188</v>
       </c>
       <c r="AG3">
-        <v>28.58100813675254</v>
+        <v>44.31671144313188</v>
       </c>
       <c r="AH3">
-        <v>0.2209192072794169</v>
+        <v>0.3232117369162425</v>
       </c>
       <c r="AI3">
-        <v>0.4151745152310913</v>
+        <v>0.584936336690645</v>
       </c>
       <c r="AJ3">
-        <v>0.1678461294626536</v>
+        <v>0.2597442599161985</v>
       </c>
       <c r="AK3">
-        <v>0.3355326352896364</v>
+        <v>0.5087050545068036</v>
       </c>
       <c r="AL3">
-        <v>0.911</v>
+        <v>0.951</v>
       </c>
       <c r="AM3">
-        <v>0.909</v>
+        <v>0.95</v>
       </c>
       <c r="AN3">
-        <v>6.411896386312761</v>
+        <v>4.757297210127399</v>
       </c>
       <c r="AO3">
-        <v>-1.536772777167947</v>
+        <v>-4.921135646687697</v>
       </c>
       <c r="AP3">
-        <v>4.570036478534146</v>
+        <v>3.573351995092072</v>
       </c>
       <c r="AQ3">
-        <v>-1.54015401540154</v>
+        <v>-4.926315789473684</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/spain/spain_software_internet.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_software_internet.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.618</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="G2">
-        <v>0.1808346213292117</v>
+        <v>0.1551020408163265</v>
       </c>
       <c r="H2">
-        <v>0.1808346213292117</v>
+        <v>0.1551020408163265</v>
       </c>
       <c r="I2">
-        <v>-0.06555397664028401</v>
+        <v>-0.019433091842255</v>
       </c>
       <c r="J2">
-        <v>-0.06555397664028401</v>
+        <v>-0.019433091842255</v>
       </c>
       <c r="K2">
-        <v>-6.83</v>
+        <v>-4.79</v>
       </c>
       <c r="L2">
-        <v>-0.105564142194745</v>
+        <v>-0.06517006802721088</v>
       </c>
       <c r="M2">
-        <v>0.55</v>
+        <v>0.019</v>
       </c>
       <c r="N2">
-        <v>0.00435471100554236</v>
+        <v>0.0002142051860202931</v>
       </c>
       <c r="O2">
-        <v>-0.08052708638360176</v>
+        <v>-0.003966597077244258</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.55</v>
+        <v>0.019</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>16</v>
+        <v>11.1</v>
       </c>
       <c r="V2">
-        <v>0.1266825019794141</v>
+        <v>0.125140924464487</v>
       </c>
       <c r="W2">
-        <v>-0.1206713780918728</v>
+        <v>-0.1119158878504673</v>
       </c>
       <c r="X2">
-        <v>0.1878682728384909</v>
+        <v>0.1833215712254748</v>
       </c>
       <c r="Y2">
-        <v>-0.3085396509303637</v>
+        <v>-0.2952374590759421</v>
       </c>
       <c r="Z2">
-        <v>1.847689212765585</v>
+        <v>1.376361676336572</v>
       </c>
       <c r="AA2">
-        <v>-0.1211233754921399</v>
+        <v>-0.02674696286440866</v>
       </c>
       <c r="AB2">
-        <v>0.14335396086642</v>
+        <v>0.1201209221766709</v>
       </c>
       <c r="AC2">
-        <v>-0.2644773363585599</v>
+        <v>-0.1468678850410796</v>
       </c>
       <c r="AD2">
-        <v>59</v>
+        <v>76.2</v>
       </c>
       <c r="AE2">
-        <v>1.316711443131878</v>
+        <v>0.3016612520287131</v>
       </c>
       <c r="AF2">
-        <v>60.31671144313188</v>
+        <v>76.50166125202871</v>
       </c>
       <c r="AG2">
-        <v>44.31671144313188</v>
+        <v>65.40166125202872</v>
       </c>
       <c r="AH2">
-        <v>0.3232117369162425</v>
+        <v>0.4630804597982773</v>
       </c>
       <c r="AI2">
-        <v>0.584936336690645</v>
+        <v>0.6285999752591993</v>
       </c>
       <c r="AJ2">
-        <v>0.2597442599161985</v>
+        <v>0.4244059455340084</v>
       </c>
       <c r="AK2">
-        <v>0.5087050545068036</v>
+        <v>0.5913262107609535</v>
       </c>
       <c r="AL2">
-        <v>0.951</v>
+        <v>1.18</v>
       </c>
       <c r="AM2">
-        <v>0.95</v>
+        <v>1.156</v>
       </c>
       <c r="AN2">
-        <v>4.757297210127399</v>
+        <v>7.146876758581879</v>
       </c>
       <c r="AO2">
-        <v>-4.921135646687697</v>
+        <v>-1.296610169491526</v>
       </c>
       <c r="AP2">
-        <v>3.573351995092072</v>
+        <v>6.134089406493032</v>
       </c>
       <c r="AQ2">
-        <v>-4.926315789473684</v>
+        <v>-1.323529411764706</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +719,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.618</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="G3">
-        <v>0.1808346213292117</v>
+        <v>0.1551020408163265</v>
       </c>
       <c r="H3">
-        <v>0.1808346213292117</v>
+        <v>0.1551020408163265</v>
       </c>
       <c r="I3">
-        <v>-0.06555397664028401</v>
+        <v>-0.019433091842255</v>
       </c>
       <c r="J3">
-        <v>-0.06555397664028401</v>
+        <v>-0.019433091842255</v>
       </c>
       <c r="K3">
-        <v>-6.83</v>
+        <v>-4.79</v>
       </c>
       <c r="L3">
-        <v>-0.105564142194745</v>
+        <v>-0.06517006802721088</v>
       </c>
       <c r="M3">
-        <v>0.55</v>
+        <v>0.019</v>
       </c>
       <c r="N3">
-        <v>0.00435471100554236</v>
+        <v>0.0002142051860202931</v>
       </c>
       <c r="O3">
-        <v>-0.08052708638360176</v>
+        <v>-0.003966597077244258</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +758,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.55</v>
+        <v>0.019</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>16</v>
+        <v>11.1</v>
       </c>
       <c r="V3">
-        <v>0.1266825019794141</v>
+        <v>0.125140924464487</v>
       </c>
       <c r="W3">
-        <v>-0.1206713780918728</v>
+        <v>-0.1119158878504673</v>
       </c>
       <c r="X3">
-        <v>0.1878682728384909</v>
+        <v>0.1833215712254748</v>
       </c>
       <c r="Y3">
-        <v>-0.3085396509303637</v>
+        <v>-0.2952374590759421</v>
       </c>
       <c r="Z3">
-        <v>1.847689212765585</v>
+        <v>1.376361676336572</v>
       </c>
       <c r="AA3">
-        <v>-0.1211233754921399</v>
+        <v>-0.02674696286440866</v>
       </c>
       <c r="AB3">
-        <v>0.14335396086642</v>
+        <v>0.1201209221766709</v>
       </c>
       <c r="AC3">
-        <v>-0.2644773363585599</v>
+        <v>-0.1468678850410796</v>
       </c>
       <c r="AD3">
-        <v>59</v>
+        <v>76.2</v>
       </c>
       <c r="AE3">
-        <v>1.316711443131878</v>
+        <v>0.3016612520287131</v>
       </c>
       <c r="AF3">
-        <v>60.31671144313188</v>
+        <v>76.50166125202871</v>
       </c>
       <c r="AG3">
-        <v>44.31671144313188</v>
+        <v>65.40166125202872</v>
       </c>
       <c r="AH3">
-        <v>0.3232117369162425</v>
+        <v>0.4630804597982773</v>
       </c>
       <c r="AI3">
-        <v>0.584936336690645</v>
+        <v>0.6285999752591993</v>
       </c>
       <c r="AJ3">
-        <v>0.2597442599161985</v>
+        <v>0.4244059455340084</v>
       </c>
       <c r="AK3">
-        <v>0.5087050545068036</v>
+        <v>0.5913262107609535</v>
       </c>
       <c r="AL3">
-        <v>0.951</v>
+        <v>1.18</v>
       </c>
       <c r="AM3">
-        <v>0.95</v>
+        <v>1.156</v>
       </c>
       <c r="AN3">
-        <v>4.757297210127399</v>
+        <v>7.146876758581879</v>
       </c>
       <c r="AO3">
-        <v>-4.921135646687697</v>
+        <v>-1.296610169491526</v>
       </c>
       <c r="AP3">
-        <v>3.573351995092072</v>
+        <v>6.134089406493032</v>
       </c>
       <c r="AQ3">
-        <v>-4.926315789473684</v>
+        <v>-1.323529411764706</v>
       </c>
     </row>
   </sheetData>
